--- a/SwagLabs_Selenium_Sprint/src/test/resources/Propertites/SwagLab_test_cases.xlsx
+++ b/SwagLabs_Selenium_Sprint/src/test/resources/Propertites/SwagLab_test_cases.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{BE38D2C1-9E73-417E-83E6-27B448B0A662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99913E74-4D0A-4038-B7A9-8F74126B1E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,13 +22,23 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Login!$A$3:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Page'!$A$3:$J$12</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <oleSize ref="B1:E4"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="157">
   <si>
     <t>Test Cases</t>
   </si>
@@ -560,6 +575,12 @@
   </si>
   <si>
     <t>User should not proceed and an appropriate validation message should be displayed</t>
+  </si>
+  <si>
+    <t>passed as expected</t>
+  </si>
+  <si>
+    <t>passed</t>
   </si>
 </sst>
 </file>
@@ -589,12 +610,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -624,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -632,7 +665,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -978,34 +1014,34 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1034,8 +1070,12 @@
       <c r="H4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="64.95" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -1062,8 +1102,12 @@
       <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="64.95" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -1090,8 +1134,12 @@
       <c r="H6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="64.95" customHeight="1">
       <c r="A7" s="2" t="s">
@@ -1118,8 +1166,12 @@
       <c r="H7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="64.95" customHeight="1">
       <c r="A8" s="2" t="s">
@@ -1146,8 +1198,12 @@
       <c r="H8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="64.95" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1174,8 +1230,12 @@
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="64.95" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -1202,8 +1262,12 @@
       <c r="H10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="64.95" customHeight="1">
       <c r="A11" s="2" t="s">
@@ -1230,8 +1294,12 @@
       <c r="H11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="64.95" customHeight="1">
       <c r="A12" s="2" t="s">
@@ -1258,8 +1326,12 @@
       <c r="H12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:J12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1310,34 +1382,34 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1366,8 +1438,12 @@
       <c r="H4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="64.95" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -1394,8 +1470,12 @@
       <c r="H5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="64.95" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -1422,8 +1502,12 @@
       <c r="H6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="64.95" customHeight="1">
       <c r="A7" s="2" t="s">
@@ -1450,8 +1534,12 @@
       <c r="H7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="64.95" customHeight="1">
       <c r="A8" s="2" t="s">
@@ -1478,8 +1566,12 @@
       <c r="H8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="64.95" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1506,8 +1598,12 @@
       <c r="H9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="64.95" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -1534,8 +1630,12 @@
       <c r="H10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="64.95" customHeight="1">
       <c r="A11" s="2" t="s">
@@ -1562,8 +1662,12 @@
       <c r="H11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="64.95" customHeight="1">
       <c r="A12" s="2" t="s">
@@ -1590,8 +1694,12 @@
       <c r="H12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:J12" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -1642,34 +1750,34 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1698,8 +1806,12 @@
       <c r="H4" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="64.95" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -1726,8 +1838,12 @@
       <c r="H5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="64.95" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -1754,8 +1870,12 @@
       <c r="H6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="64.95" customHeight="1">
       <c r="A7" s="2" t="s">
@@ -1782,8 +1902,12 @@
       <c r="H7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="64.95" customHeight="1">
       <c r="A8" s="2" t="s">
@@ -1810,8 +1934,12 @@
       <c r="H8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="64.95" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1838,8 +1966,12 @@
       <c r="H9" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="64.95" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -1866,8 +1998,12 @@
       <c r="H10" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="64.95" customHeight="1">
       <c r="A11" s="2" t="s">
@@ -1894,8 +2030,12 @@
       <c r="H11" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="64.95" customHeight="1">
       <c r="A12" s="2" t="s">
@@ -1922,8 +2062,12 @@
       <c r="H12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="64.95" customHeight="1">
       <c r="A13" s="2" t="s">
@@ -1950,8 +2094,12 @@
       <c r="H13" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="64.95" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1978,8 +2126,12 @@
       <c r="H14" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="64.95" customHeight="1">
       <c r="A15" s="2" t="s">
@@ -2006,8 +2158,12 @@
       <c r="H15" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="64.95" customHeight="1">
       <c r="A16" s="2" t="s">
@@ -2034,8 +2190,12 @@
       <c r="H16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:J16" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
